--- a/ko/103-law-textbook/_workspace/상속증여세법/원문대조_작업표.xlsx
+++ b/ko/103-law-textbook/_workspace/상속증여세법/원문대조_작업표.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="① 작업표" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="② 요약" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="③ 확인 방법" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="④ 확인 완료 이력" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="⑤ 조문 인용 색인" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="⑥ 핵심 수치 30선" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="① 작업표" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="② 요약" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="③ 확인 방법" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="④ 확인 완료 이력" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑤ 조문 인용 색인" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑥ 핵심 수치 30선" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'① 작업표'!$A$1:$N$155</definedName>
